--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
 This element is labeled as a modifier because the status contains the code entered-in-error that mark the Appointment as not currently valid.</t>
   </si>
   <si>
-    <t>booked</t>
+    <t>fulfilled</t>
   </si>
   <si>
     <t>The free/busy status of an appointment.</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T18:46:21+00:00</t>
+    <t>2023-02-07T12:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$42</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="356">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -504,242 +504,53 @@
     <t>SCH-1, SCH-2, ARQ-1, ARQ-2</t>
   </si>
   <si>
-    <t>Appointment.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Appointment.identifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Appointment.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>Appointment.status</t>
+  </si>
+  <si>
+    <t>proposed | pending | booked | arrived | fulfilled | cancelled | noshow | entered-in-error | checked-in | waitlist</t>
+  </si>
+  <si>
+    <t>The overall status of the Appointment. Each of the participants has their own participation status which indicates their involvement in the process, however this status indicates the shared status.</t>
+  </si>
+  <si>
+    <t>If the Appointment's status is "cancelled" then all participants are expected to have their calendars released for the appointment period, and as such any Slots that were marked as BUSY can be re-set to FREE.
+This element is labeled as a modifier because the status contains the code entered-in-error that mark the Appointment as not currently valid.</t>
+  </si>
+  <si>
+    <t>fulfilled</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Appointment.identifier.type</t>
+    <t>The free/busy status of an appointment.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/appointmentstatus|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.status</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>SCH-25</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Appointment.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>Appointment.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>Appointment.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Appointment.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>Appointment.status</t>
-  </si>
-  <si>
-    <t>proposed | pending | booked | arrived | fulfilled | cancelled | noshow | entered-in-error | checked-in | waitlist</t>
-  </si>
-  <si>
-    <t>The overall status of the Appointment. Each of the participants has their own participation status which indicates their involvement in the process, however this status indicates the shared status.</t>
-  </si>
-  <si>
-    <t>If the Appointment's status is "cancelled" then all participants are expected to have their calendars released for the appointment period, and as such any Slots that were marked as BUSY can be re-set to FREE.
-This element is labeled as a modifier because the status contains the code entered-in-error that mark the Appointment as not currently valid.</t>
-  </si>
-  <si>
-    <t>fulfilled</t>
-  </si>
-  <si>
-    <t>The free/busy status of an appointment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/appointmentstatus|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.status</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>SCH-25</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason</t>
-  </si>
-  <si>
     <t>The coded reason for the appointment being cancelled</t>
   </si>
   <si>
@@ -750,6 +561,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason</t>
+  </si>
+  <si>
+    <t>n/a</t>
   </si>
   <si>
     <t>Appointment.serviceCategory</t>
@@ -903,6 +717,10 @@
     <t>Appointment.description</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Shown on a subject line in a meeting request, or appointment list</t>
   </si>
   <si>
@@ -1142,7 +960,25 @@
     <t>Appointment.participant.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>Appointment.participant.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>Appointment.participant.modifierExtension</t>
@@ -1178,6 +1014,9 @@
 This value SHALL be the same when creating an AppointmentResponse so that they can be matched, and subsequently update the Appointment.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Role of participant in encounter.</t>
   </si>
   <si>
@@ -1261,6 +1100,10 @@
   </si>
   <si>
     <t>Appointment.participant.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
   </si>
   <si>
     <t>Participation period of the actor</t>
@@ -1594,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.66796875" customWidth="true" bestFit="true"/>
@@ -1620,11 +1463,11 @@
     <col min="21" max="21" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="50.4921875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="56.640625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
@@ -3009,7 +2852,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>147</v>
       </c>
@@ -3019,13 +2862,13 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -3121,7 +2964,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>156</v>
       </c>
@@ -3131,30 +2974,32 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K14" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="K14" t="s" s="2">
+      <c r="L14" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
         <v>74</v>
@@ -3164,7 +3009,7 @@
         <v>74</v>
       </c>
       <c r="R14" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>74</v>
@@ -3179,13 +3024,13 @@
         <v>74</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="Z14" t="s" s="2">
         <v>74</v>
@@ -3203,10 +3048,10 @@
         <v>74</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>83</v>
@@ -3215,38 +3060,38 @@
         <v>74</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>74</v>
@@ -3255,20 +3100,18 @@
         <v>74</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
         <v>74</v>
@@ -3293,49 +3136,47 @@
         <v>74</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="X15" s="2"/>
       <c r="Y15" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="Z15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="AC15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>74</v>
@@ -3349,7 +3190,7 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3360,32 +3201,28 @@
         <v>75</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
         <v>74</v>
       </c>
@@ -3409,13 +3246,11 @@
         <v>74</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="X16" t="s" s="2">
         <v>173</v>
       </c>
+      <c r="X16" s="2"/>
       <c r="Y16" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="Z16" t="s" s="2">
         <v>74</v>
@@ -3433,13 +3268,13 @@
         <v>74</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>74</v>
@@ -3451,21 +3286,21 @@
         <v>74</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>126</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3476,7 +3311,7 @@
         <v>75</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>74</v>
@@ -3488,20 +3323,18 @@
         <v>84</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
         <v>74</v>
       </c>
@@ -3525,13 +3358,11 @@
         <v>74</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="X17" s="2"/>
       <c r="Y17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>74</v>
@@ -3549,13 +3380,13 @@
         <v>74</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>74</v>
@@ -3564,10 +3395,10 @@
         <v>95</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>74</v>
@@ -3576,7 +3407,7 @@
         <v>74</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>187</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -3592,7 +3423,7 @@
         <v>75</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>74</v>
@@ -3604,7 +3435,7 @@
         <v>84</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>189</v>
@@ -3612,12 +3443,8 @@
       <c r="L18" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
         <v>74</v>
       </c>
@@ -3629,7 +3456,7 @@
         <v>74</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>193</v>
+        <v>74</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>74</v>
@@ -3641,13 +3468,11 @@
         <v>74</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="X18" s="2"/>
       <c r="Y18" t="s" s="2">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>74</v>
@@ -3665,13 +3490,13 @@
         <v>74</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>74</v>
@@ -3683,21 +3508,21 @@
         <v>74</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>74</v>
+        <v>193</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>196</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3705,13 +3530,13 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -3720,17 +3545,15 @@
         <v>84</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
         <v>74</v>
@@ -3743,7 +3566,7 @@
         <v>74</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>201</v>
+        <v>74</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>74</v>
@@ -3755,13 +3578,11 @@
         <v>74</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="X19" s="2"/>
       <c r="Y19" t="s" s="2">
-        <v>74</v>
+        <v>197</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>74</v>
@@ -3779,7 +3600,7 @@
         <v>74</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>75</v>
@@ -3797,21 +3618,21 @@
         <v>74</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>74</v>
+        <v>199</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -3822,7 +3643,7 @@
         <v>75</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>74</v>
@@ -3834,13 +3655,13 @@
         <v>84</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -3867,13 +3688,13 @@
         <v>74</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>74</v>
+        <v>204</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>74</v>
+        <v>205</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>74</v>
@@ -3891,13 +3712,13 @@
         <v>74</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>74</v>
@@ -3906,10 +3727,10 @@
         <v>95</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>74</v>
+        <v>206</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>74</v>
@@ -3918,12 +3739,12 @@
         <v>74</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -3934,7 +3755,7 @@
         <v>75</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>74</v>
@@ -3943,20 +3764,18 @@
         <v>74</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
         <v>74</v>
@@ -4005,13 +3824,13 @@
         <v>74</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>74</v>
@@ -4020,10 +3839,10 @@
         <v>95</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>74</v>
@@ -4032,12 +3851,12 @@
         <v>74</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4045,31 +3864,31 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>103</v>
+        <v>216</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
@@ -4080,7 +3899,7 @@
         <v>74</v>
       </c>
       <c r="R22" t="s" s="2">
-        <v>224</v>
+        <v>74</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>74</v>
@@ -4095,13 +3914,13 @@
         <v>74</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>226</v>
+        <v>74</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>74</v>
@@ -4119,10 +3938,10 @@
         <v>74</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4134,24 +3953,24 @@
         <v>95</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4171,16 +3990,16 @@
         <v>74</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -4207,11 +4026,13 @@
         <v>74</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="X23" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Y23" t="s" s="2">
-        <v>236</v>
+        <v>74</v>
       </c>
       <c r="Z23" t="s" s="2">
         <v>74</v>
@@ -4229,7 +4050,7 @@
         <v>74</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>75</v>
@@ -4247,21 +4068,21 @@
         <v>74</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>74</v>
+        <v>229</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>74</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4281,16 +4102,16 @@
         <v>74</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -4317,11 +4138,13 @@
         <v>74</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="X24" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Y24" t="s" s="2">
-        <v>240</v>
+        <v>74</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>74</v>
@@ -4339,7 +4162,7 @@
         <v>74</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>75</v>
@@ -4354,24 +4177,24 @@
         <v>95</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4382,10 +4205,10 @@
         <v>75</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -4394,17 +4217,15 @@
         <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>74</v>
@@ -4429,11 +4250,13 @@
         <v>74</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="X25" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Y25" t="s" s="2">
-        <v>247</v>
+        <v>74</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>74</v>
@@ -4451,13 +4274,13 @@
         <v>74</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>74</v>
@@ -4466,24 +4289,24 @@
         <v>95</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>74</v>
+        <v>245</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>74</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4494,7 +4317,7 @@
         <v>75</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>74</v>
@@ -4506,13 +4329,13 @@
         <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4539,11 +4362,13 @@
         <v>74</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="X26" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Y26" t="s" s="2">
-        <v>252</v>
+        <v>74</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>74</v>
@@ -4561,13 +4386,13 @@
         <v>74</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>74</v>
@@ -4576,19 +4401,19 @@
         <v>95</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>74</v>
+        <v>243</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>74</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -4613,16 +4438,16 @@
         <v>74</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -4649,11 +4474,13 @@
         <v>74</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="X27" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Y27" t="s" s="2">
-        <v>258</v>
+        <v>74</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>74</v>
@@ -4686,7 +4513,7 @@
         <v>95</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>74</v>
+        <v>243</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>259</v>
@@ -4698,12 +4525,12 @@
         <v>74</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>261</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4723,10 +4550,10 @@
         <v>74</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>178</v>
+        <v>262</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>263</v>
@@ -4759,13 +4586,13 @@
         <v>74</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>266</v>
+        <v>74</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>74</v>
@@ -4783,7 +4610,7 @@
         <v>74</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>75</v>
@@ -4798,10 +4625,10 @@
         <v>95</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>267</v>
+        <v>74</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>74</v>
@@ -4810,12 +4637,12 @@
         <v>74</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -4826,7 +4653,7 @@
         <v>75</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>74</v>
@@ -4838,15 +4665,17 @@
         <v>74</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M29" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
         <v>74</v>
@@ -4895,13 +4724,13 @@
         <v>74</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>74</v>
@@ -4910,13 +4739,13 @@
         <v>95</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>74</v>
+        <v>273</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>74</v>
@@ -4927,7 +4756,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -4950,16 +4779,16 @@
         <v>74</v>
       </c>
       <c r="J30" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
@@ -5009,7 +4838,7 @@
         <v>74</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>75</v>
@@ -5024,24 +4853,24 @@
         <v>95</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>254</v>
+        <v>74</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>284</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5064,13 +4893,13 @@
         <v>74</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -5121,7 +4950,7 @@
         <v>74</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>75</v>
@@ -5139,35 +4968,35 @@
         <v>74</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>290</v>
+        <v>230</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>74</v>
+        <v>286</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>74</v>
@@ -5176,13 +5005,13 @@
         <v>74</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5233,7 +5062,7 @@
         <v>74</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>75</v>
@@ -5248,24 +5077,24 @@
         <v>95</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>297</v>
+        <v>74</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>298</v>
+        <v>74</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5273,28 +5102,28 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -5345,39 +5174,39 @@
         <v>74</v>
       </c>
       <c r="AE33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AF33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="AM33" t="s" s="2">
-        <v>306</v>
+        <v>74</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5397,16 +5226,16 @@
         <v>74</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -5457,7 +5286,7 @@
         <v>74</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>75</v>
@@ -5469,38 +5298,38 @@
         <v>74</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>303</v>
+        <v>74</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>311</v>
+        <v>175</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>312</v>
+        <v>74</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>313</v>
+        <v>74</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>314</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>74</v>
@@ -5512,15 +5341,17 @@
         <v>74</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>316</v>
+        <v>128</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="M35" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
         <v>74</v>
@@ -5569,28 +5400,28 @@
         <v>74</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>303</v>
+        <v>74</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>319</v>
+        <v>175</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>320</v>
+        <v>74</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>74</v>
@@ -5601,11 +5432,11 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>74</v>
+        <v>310</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5618,22 +5449,26 @@
         <v>74</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>322</v>
+        <v>128</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O36" t="s" s="2">
         <v>74</v>
       </c>
@@ -5681,7 +5516,7 @@
         <v>74</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>75</v>
@@ -5693,13 +5528,13 @@
         <v>74</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>325</v>
+        <v>126</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>74</v>
@@ -5713,7 +5548,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5724,7 +5559,7 @@
         <v>75</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>74</v>
@@ -5733,19 +5568,19 @@
         <v>74</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>327</v>
+        <v>170</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
@@ -5771,13 +5606,13 @@
         <v>74</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>74</v>
+        <v>318</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>74</v>
+        <v>319</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>74</v>
+        <v>320</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>74</v>
@@ -5795,13 +5630,13 @@
         <v>74</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>74</v>
@@ -5810,24 +5645,24 @@
         <v>95</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>331</v>
+        <v>74</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>333</v>
+        <v>175</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>74</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -5847,20 +5682,18 @@
         <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>157</v>
+        <v>324</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
         <v>74</v>
@@ -5909,7 +5742,7 @@
         <v>74</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>75</v>
@@ -5924,24 +5757,24 @@
         <v>95</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>338</v>
+        <v>74</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>74</v>
+        <v>329</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>290</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -5961,16 +5794,16 @@
         <v>74</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -5997,13 +5830,13 @@
         <v>74</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>74</v>
+        <v>334</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>74</v>
+        <v>335</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>74</v>
@@ -6021,7 +5854,7 @@
         <v>74</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>75</v>
@@ -6039,25 +5872,25 @@
         <v>74</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>290</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>346</v>
+        <v>74</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6067,22 +5900,22 @@
         <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I40" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="J40" t="s" s="2">
-        <v>347</v>
+        <v>103</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6109,13 +5942,13 @@
         <v>74</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>74</v>
+        <v>341</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>74</v>
+        <v>342</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>74</v>
@@ -6133,13 +5966,13 @@
         <v>74</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>74</v>
@@ -6148,24 +5981,24 @@
         <v>95</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>350</v>
+        <v>74</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>74</v>
+        <v>344</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>74</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6173,11 +6006,11 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F41" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="F41" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="G41" t="s" s="2">
         <v>74</v>
       </c>
@@ -6188,13 +6021,13 @@
         <v>74</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -6245,39 +6078,39 @@
         <v>74</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG41" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AG41" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AH41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>356</v>
+        <v>95</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>357</v>
+        <v>74</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>358</v>
+        <v>175</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>359</v>
+        <v>74</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>360</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6288,7 +6121,7 @@
         <v>75</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>74</v>
@@ -6300,15 +6133,17 @@
         <v>74</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>157</v>
+        <v>347</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>158</v>
+        <v>351</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M42" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
         <v>74</v>
@@ -6357,25 +6192,25 @@
         <v>74</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>160</v>
+        <v>350</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>74</v>
+        <v>243</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>161</v>
+        <v>354</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>74</v>
@@ -6384,917 +6219,11 @@
         <v>74</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="B43" s="2"/>
-      <c r="C43" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P43" s="2"/>
-      <c r="Q43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B44" s="2"/>
-      <c r="C44" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="D44" s="2"/>
-      <c r="E44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P44" s="2"/>
-      <c r="Q44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="B45" s="2"/>
-      <c r="C45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D45" s="2"/>
-      <c r="E45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P45" s="2"/>
-      <c r="Q45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="B46" s="2"/>
-      <c r="C46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D46" s="2"/>
-      <c r="E46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P46" s="2"/>
-      <c r="Q46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D47" s="2"/>
-      <c r="E47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P47" s="2"/>
-      <c r="Q47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D48" s="2"/>
-      <c r="E48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="F48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P48" s="2"/>
-      <c r="Q48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="C49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D49" s="2"/>
-      <c r="E49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P49" s="2"/>
-      <c r="Q49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="B50" s="2"/>
-      <c r="C50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D50" s="2"/>
-      <c r="E50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P50" s="2"/>
-      <c r="Q50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>407</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN50">
+  <autoFilter ref="A1:AN42">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7304,7 +6233,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI49">
+  <conditionalFormatting sqref="A2:AI41">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
